--- a/assets/libreoffice_calc_njc/8c891b4d-2e1e-4a79-9a4d-2e326c6d5ae9/Product_Gross_Margin.xlsx
+++ b/assets/libreoffice_calc_njc/8c891b4d-2e1e-4a79-9a4d-2e326c6d5ae9/Product_Gross_Margin.xlsx
@@ -209,7 +209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
